--- a/dietitian_forms/010_meal_planning_form--dietitian_forms.xlsx
+++ b/dietitian_forms/010_meal_planning_form--dietitian_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>meal_planning_form_1</t>
+          <t>general_info</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>What type of meals do you typically eat?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>meal_planning_form_2</t>
+          <t>dietary_preferences</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>food_preferences</t>
+          <t>What are your dietary preferences?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>meal_planning_form_3</t>
+          <t>allergies</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dietary_restrictions</t>
+          <t>Do you have any food allergies or intolerances?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>meal_planning_form_4</t>
+          <t>planning_goals</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>meal_preferences</t>
+          <t>What are your meal planning goals?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,40 +607,40 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>meal_planning_form_5</t>
+          <t>favorites</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>meal_preferences</t>
+          <t>What are your favorite foods or cuisines?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>meal_planning_form_6</t>
+          <t>restrictions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>Do you have any specific dietary restrictions?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>meal_planning_form_7</t>
+          <t>eating_out</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dietary_restrictions</t>
+          <t>How often do you eat out or order takeout?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>meal_planning_form_8</t>
+          <t>planning_method</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>What is your preferred method of meal planning?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>meal_planning_form_9</t>
+          <t>needs</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>food_preferences</t>
+          <t>Do you have any specific dietary needs or concerns?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>meal_planning_form_10</t>
+          <t>meals_per_day</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dietary_restrictions</t>
+          <t>How many meals do you typically eat per day?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>meal_planning_form_11</t>
+          <t>cooking_method</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>Do you have a preferred cooking method?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,90 +768,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>meal_planning_form_12</t>
+          <t>planning_schedule</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>food_preferences</t>
+          <t>Do you have any specific meal planning schedules?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>meal_planning_form_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>dietary_restrictions</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>meal_planning_form_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>first_page</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>meal_planning_form_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>food_preferences</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -868,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -896,306 +827,527 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>meal_planning_form_2_choices</t>
+          <t>general_info_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option_1',_'label':_'option_1'}</t>
+          <t>breakfast</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'option_1', 'label': 'option_1'}</t>
+          <t>Breakfast</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>meal_planning_form_2_choices</t>
+          <t>general_info_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option_2',_'label':_'option_2'}</t>
+          <t>lunch</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'option_2', 'label': 'option_2'}</t>
+          <t>Lunch</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>meal_planning_form_2_choices</t>
+          <t>general_info_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'option_3',_'label':_'option_3'}</t>
+          <t>dinner</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'option_3', 'label': 'option_3'}</t>
+          <t>Dinner</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>meal_planning_form_3_choices</t>
+          <t>general_info_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option_1',_'label':_'option_1'}</t>
+          <t>snacks</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'option_1', 'label': 'option_1'}</t>
+          <t>Snacks</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>meal_planning_form_3_choices</t>
+          <t>dietary_preferences_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option_2',_'label':_'option_2'}</t>
+          <t>vegan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'option_2', 'label': 'option_2'}</t>
+          <t>Vegan</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>meal_planning_form_3_choices</t>
+          <t>dietary_preferences_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'option_3',_'label':_'option_3'}</t>
+          <t>gluten-free</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'option_3', 'label': 'option_3'}</t>
+          <t>Gluten-free</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>meal_planning_form_7_choices</t>
+          <t>dietary_preferences_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'option_4',_'label':_'option_4'}</t>
+          <t>dairy-free</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'option_4', 'label': 'option_4'}</t>
+          <t>Dairy-free</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>meal_planning_form_7_choices</t>
+          <t>dietary_preferences_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'option_5',_'label':_'option_5'}</t>
+          <t>low-carb</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'option_5', 'label': 'option_5'}</t>
+          <t>Low-carb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>meal_planning_form_7_choices</t>
+          <t>planning_goals_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'option_6',_'label':_'option_6'}</t>
+          <t>weight_loss</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'option_6', 'label': 'option_6'}</t>
+          <t>Weight Loss</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>meal_planning_form_9_choices</t>
+          <t>planning_goals_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'option_7',_'label':_'option_7'}</t>
+          <t>weight_gain</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'option_7', 'label': 'option_7'}</t>
+          <t>Weight Gain</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>meal_planning_form_9_choices</t>
+          <t>planning_goals_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'option_8',_'label':_'option_8'}</t>
+          <t>health_maintenance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'option_8', 'label': 'option_8'}</t>
+          <t>Health Maintenance</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>meal_planning_form_9_choices</t>
+          <t>favorites_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'option_9',_'label':_'option_9'}</t>
+          <t>italian</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'option_9', 'label': 'option_9'}</t>
+          <t>Italian</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>meal_planning_form_10_choices</t>
+          <t>favorites_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'option_10',_'label':_'option_10'}</t>
+          <t>mexican</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'option_10', 'label': 'option_10'}</t>
+          <t>Mexican</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>meal_planning_form_10_choices</t>
+          <t>favorites_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'option_11',_'label':_'option_11'}</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'option_11', 'label': 'option_11'}</t>
+          <t>Indian</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>meal_planning_form_10_choices</t>
+          <t>restrictions_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'option_12',_'label':_'option_12'}</t>
+          <t>vegetarian</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'option_12', 'label': 'option_12'}</t>
+          <t>Vegetarian</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>meal_planning_form_13_choices</t>
+          <t>restrictions_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'option_13',_'label':_'option_13'}</t>
+          <t>low_sodium</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'option_13', 'label': 'option_13'}</t>
+          <t>Low Sodium</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>meal_planning_form_13_choices</t>
+          <t>eating_out_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'option_14',_'label':_'option_14'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'option_14', 'label': 'option_14'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>meal_planning_form_13_choices</t>
+          <t>eating_out_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_'option_15',_'label':_'option_15'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': 'option_15', 'label': 'option_15'}</t>
+          <t>Occasionally</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>eating_out_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>often</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Often</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>planning_method_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>planning_method_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>cookbook</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Cookbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>planning_method_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>online_recipes</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Online Recipes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>needs_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>diabetes</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Diabetes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>needs_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>kidney_disease</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Kidney Disease</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>needs_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cooking_method_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>baking</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Baking</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cooking_method_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>grilling</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Grilling</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cooking_method_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>sautéing</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Sautéing</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>planning_schedule_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>meal_prep</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Meal Prep</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>planning_schedule_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>batch_cooking</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Batch Cooking</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>planning_schedule_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
